--- a/02_DIA_inicio_2026_analisis_assets/rbd_9593_escuela-basica-educadores-de-chile_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9593_escuela-basica-educadores-de-chile_nt1_nucleos.xlsx
@@ -727,13 +727,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9F4CDCC-F7ED-4510-A6A7-E3CE942DF623}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0693696-185C-4E44-A2FE-10EEA3E4E00C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64A53D88-B452-4537-9F20-BD1986499E8B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B06ADA5-611A-46FA-8D38-79007A5278A4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E755AEC-D05A-447E-9652-619B3941FE7F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F063696C-1819-4241-8689-0285AFB01E95}"/>
 </file>